--- a/reports/worklog.xlsx
+++ b/reports/worklog.xlsx
@@ -2,24 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14760" yWindow="4680" windowWidth="33375" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="worklog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +31,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -42,8 +43,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,16 +59,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -82,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,9 +127,31 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -465,401 +514,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="95" customWidth="1" min="4" max="4"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>День недели</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Направление</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Задача</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Часы (оц.)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Четверг</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Пятница</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Аналитика</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Анализ протокола relay.link: API quote/execute/status, currencies, механика step-execution</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="12" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Четверг</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Пятница</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Аналитика</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Исследование сети Abstract (zkSync-стек, EOA vs AGW, газовая модель) и AdsPower Local API</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Четверг</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Пятница</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Архитектура</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>PLAN.md: стек, схема SQLite, конфигурация, state machine, алгоритм обработки ошибок</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="12" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Четверг</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Пятница</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Архитектура</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Прокси-слой: формат login:passwd@ip:port, пул, ротация при сбоях, привязка к кошелькам</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Четверг</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Пятница</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Архитектура</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Переход на открытые источники: публичные RPC-пулы, Multicall3, отказ от ключевых API</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Инициализация проекта: структура src/, конфигурация .env + config.yaml, requirements</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="A8" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>БД</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>SQLite-схема и DAO: wallets/token_balances/jobs/tx_log, идемпотентные upsert-ы</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="A9" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Интеграции</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Relay-клиент: quote/v2, intents/status/v3, currencies/v1, chains, ретраи tenacity</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="A10" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Web3</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Клиенты Abstract/Base: EIP-1559 (+legacy/zksync2 fallback), Multicall3-дискавери, watch-баланс</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="A11" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Сеть</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Пулы прокси и публичных RPC: health-check, ротация, маскирование кредов в логах</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="A12" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Ядро</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Pipeline/state machine: QUOTE→APPROVE→DEPOSIT→BRIDGE→TRANSFER, идемпотентность, ретраи</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="12" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="A13" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>CLI</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Typer-CLI: init-data/sync/discover/run/status/retry, rich-логирование</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="A14" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Тестирование</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Живые смоук/E2E-тесты на публичных API; фиксы: валидация адресов, no-route → SKIPPED</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Пятница</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="A15" s="9" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>суббота</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Документация</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>README, CLAUDE.md для ИИ-агентов, актуализация PLAN.md, файл отчётности</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="D16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Функционал</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Очередь без адреса: статус WAITING_TARGET — задача ждёт target_address и стартует при его появлении</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Синхронизация</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>XLSX как источник истины: добавление/удаление кошельков в БД по файлу, каскадное удаление задач, защита от обнуления</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Тестирование</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Реальный прогон на боевом кошельке через прокси + диагностика балансов (EOA Abstract пуст, только скам-токены)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Тестирование</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Детерминированные тесты новых сценариев sync: add / delete-cascade / target-fill / защита (6 проверок)</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Документация</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Обновление PLAN.md / README / CLAUDE.md под новое поведение; актуализация отчётности</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Итого часов</t>
         </is>
       </c>
-      <c r="E16" s="6">
-        <f>SUM(E2:E15)</f>
+      <c r="E21" s="14">
+        <f>SUM(E2:E20)</f>
         <v/>
       </c>
     </row>

--- a/reports/worklog.xlsx
+++ b/reports/worklog.xlsx
@@ -17,8 +17,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,7 +133,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -148,6 +148,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -552,7 +555,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="15" t="n">
         <v>46213</v>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -575,7 +578,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="15" t="n">
         <v>46213</v>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -598,7 +601,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="15" t="n">
         <v>46213</v>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -621,7 +624,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="15" t="n">
         <v>46213</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -644,7 +647,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="15" t="n">
         <v>46213</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -667,7 +670,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -690,7 +693,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -713,7 +716,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -736,7 +739,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -759,7 +762,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -782,7 +785,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -805,7 +808,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -828,7 +831,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -851,7 +854,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -874,7 +877,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -897,7 +900,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -920,7 +923,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -943,7 +946,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -966,7 +969,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -989,13 +992,128 @@
       </c>
     </row>
     <row r="21">
-      <c r="D21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Диагностика</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>AGW-диагностика: средства в Abstract Global Wallet; деривация EOA/AGW-адресов, проверка k1-подписантов on-chain</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Изучение relay.link + Privy cross-app: сайт, API, структура сессии (Dynamic SDK, privy-caw), механика подписи</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>PoC браузерного входа ОДНИМ ключом (Playwright + инжектируемый window.ethereum, без расширения) — успешная валидация</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Браузер-модуль</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>src/browser: wallet_provider (инжект-провайдер) + relay_flow (login проверен, bridge-форма — каркас)</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Документация</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Обновление PLAN.md §7, CLAUDE.md, память под AGW/браузерную ветку; отчётность</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Итого часов</t>
         </is>
       </c>
-      <c r="E21" s="14">
-        <f>SUM(E2:E20)</f>
+      <c r="E26" s="14">
+        <f>SUM(E2:E25)</f>
         <v/>
       </c>
     </row>

--- a/reports/worklog.xlsx
+++ b/reports/worklog.xlsx
@@ -18,8 +18,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -134,7 +134,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,6 +149,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -553,7 +556,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -576,7 +579,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -599,7 +602,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -622,7 +625,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -645,7 +648,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -668,7 +671,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -691,7 +694,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="15" t="n">
         <v>46214</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -714,7 +717,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -737,7 +740,7 @@
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -783,7 +786,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -806,7 +809,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -829,7 +832,7 @@
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -852,7 +855,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -875,7 +878,7 @@
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -898,7 +901,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -921,7 +924,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -944,7 +947,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="15" t="n">
         <v>46215</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -967,13 +970,128 @@
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>вторник</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Исследование DeBank: структура портфеля, внутренние API (project_list/cache_balance_list/used_chains), перехват ответов в Playwright</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>вторник</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Схема чекера протоколов: каталог protocols (растёт) + wallet_protocols + tokens + agw_address, миграция</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>вторник</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Чекер</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>DeBank-чекер (Playwright-перехват API, парсинг) + оркестратор (relay.link login -&gt; AGW -&gt; DeBank -&gt; БД)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>вторник</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>CLI/Отчёт</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Интерактивное меню в main.py, цветной rich-вывод (панели/таблицы протоколов), Excel-отчёт (3 листа)</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>вторник</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Тестирование</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Реальный E2E-прогон чекера: login-&gt;AGW 0xF094..a671-&gt;DeBank-&gt;протоколы(Aborean,Witty)-&gt;Excel; кэш Privy-сессии</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Итого часов</t>
         </is>
       </c>
-      <c r="E20" s="14">
-        <f>SUM(E2:E19)</f>
+      <c r="E25" s="14">
+        <f>SUM(E2:E24)</f>
         <v/>
       </c>
     </row>

--- a/reports/worklog.xlsx
+++ b/reports/worklog.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1085,13 +1085,36 @@
       </c>
     </row>
     <row r="25">
-      <c r="D25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>вторник</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Многопоточность</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Двухфазный чекер: вход последовательно (Privy не параллелится), DeBank параллельно (--threads); анти-троттлинг, кэш AGW. Excel: разделение кошельков (заливка+рамка)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Итого часов</t>
         </is>
       </c>
-      <c r="E25" s="14">
-        <f>SUM(E2:E24)</f>
+      <c r="E26" s="14">
+        <f>SUM(E2:E25)</f>
         <v/>
       </c>
     </row>
